--- a/addon_ugears/ug_base_distrib/static/xls/template_costs_distrib.xlsx
+++ b/addon_ugears/ug_base_distrib/static/xls/template_costs_distrib.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tetiana.Buhlak\Desktop\January 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PyCharmProjects\odoo_dev_16\odoo_dev\addon_ugears\ug_base_distrib\static\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5501D468-BAB5-4DE3-BCCE-A41D5F1E42C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8652" xr2:uid="{78331738-B52F-442D-9F7E-58790C02FCD1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Marketing costs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Type of marketing</t>
   </si>
@@ -70,12 +69,18 @@
   </si>
   <si>
     <t>All forms of online advertising, such as Google Ads, and other digital marketing strategies designed to increase brand visibility and drive sales</t>
+  </si>
+  <si>
+    <t>Mass Media</t>
+  </si>
+  <si>
+    <t>Marketing expenses related to traditional media channels such as television, radio, newspapers, and magazines. This includes costs for TV commercials, radio advertisements, print ads, and PR campaigns aimed at increasing brand awareness and promotion.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -101,7 +106,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -111,6 +116,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -185,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -206,6 +217,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -532,16 +552,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1F5886-0341-4477-844D-93666F240D2D}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -561,7 +581,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -570,44 +590,53 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3" ht="78" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" ht="63" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C8" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A6">
+  <conditionalFormatting sqref="A1:A7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
